--- a/data/raw/inventory/Week 32/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 32/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
         <v>21</v>
@@ -1589,13 +1589,13 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
         <v>55</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
